--- a/public/templates/examples/A-156-ScreeningCompletionRecords-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-156-ScreeningCompletionRecords-EXAMPLE-S.xlsx
@@ -18,7 +18,7 @@
   <numFmts count="0"/>
   <fonts count="9">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
@@ -303,12 +303,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>5</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1619250" cy="1619250"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -447,12 +447,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>

--- a/public/templates/examples/A-156-ScreeningCompletionRecords-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-156-ScreeningCompletionRecords-EXAMPLE-S.xlsx
@@ -3,11 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Log!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -15,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="9">
     <font>
       <name val="Aptos"/>
@@ -174,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -223,6 +228,10 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -675,7 +684,7 @@
       <c r="E6" s="17" t="n"/>
       <c r="F6" s="16" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Coverage</t>
@@ -701,7 +710,7 @@
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="8" t="n"/>
     </row>
-    <row r="11" ht="27.75" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Entry #</t>
@@ -733,7 +742,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="19.5" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>001</t>
@@ -765,7 +774,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>002</t>
@@ -797,7 +806,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="19.5" customHeight="1">
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t>003</t>
@@ -829,7 +838,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="19.5" customHeight="1">
+    <row r="15" ht="66.4" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>004</t>
@@ -957,7 +966,7 @@
       <c r="E28" s="12" t="n"/>
       <c r="F28" s="12" t="n"/>
     </row>
-    <row r="29" ht="44" customHeight="1">
+    <row r="29" ht="50.5" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Reviewed by (Director)</t>
@@ -973,15 +982,13 @@
           <t>(on file)</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
+      <c r="D29" s="21">
+        <v>46082</v>
       </c>
       <c r="E29" s="13" t="n"/>
       <c r="F29" s="13" t="n"/>
     </row>
-    <row r="30" ht="44" customHeight="1">
+    <row r="30" ht="50.5" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Approved by (Sheriff)</t>
@@ -997,10 +1004,8 @@
           <t>(on file)</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
+      <c r="D30" s="21">
+        <v>46082</v>
       </c>
       <c r="E30" s="13" t="n"/>
       <c r="F30" s="13" t="n"/>
@@ -1097,10 +1102,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
+      <c r="B46" s="20">
+        <v>46068</v>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
@@ -1115,11 +1118,11 @@
       <c r="E46" s="11" t="n"/>
       <c r="F46" s="11" t="n"/>
     </row>
-    <row r="48" ht="62" customHeight="1">
-      <c r="A48" s="2" t="n"/>
+    <row r="48">
+      <c r="A48"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="28">
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A27:F27"/>
@@ -1142,7 +1145,6 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A4:B4"/>
@@ -1151,7 +1153,7 @@
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>